--- a/source-data/Enerium_Талисманы_Финал.xlsx
+++ b/source-data/Enerium_Талисманы_Финал.xlsx
@@ -186,7 +186,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
+          <t xml:space="preserve">2026-10-06 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
         </is>
       </c>
     </row>
@@ -198,7 +198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">78f8bae1b86c1453 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">fc47f842f7aaa0ba — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «стужа»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «стужа» (−30 % скорости: цель ходит позже) не ложится на героя</t>
         </is>
       </c>
       <c r="K146" s="3" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «истечение»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «истечение» (шансы способностей и ульты ×2/3) не ложится на героя</t>
         </is>
       </c>
       <c r="K147" s="3" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «ослабление»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «ослабление» (−25 % урона) не ложится на героя</t>
         </is>
       </c>
       <c r="K148" s="3" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «запрет способностей»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «запрет способностей» (только обычная атака) не ложится на героя</t>
         </is>
       </c>
       <c r="K149" s="3" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «оглушение»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «оглушение» (пропуск хода) не ложится на героя</t>
         </is>
       </c>
       <c r="K150" s="3" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «кровотечение»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «кровотечение» (урон в начале каждого её хода) не ложится на героя</t>
         </is>
       </c>
       <c r="K151" s="3" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «метка»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «метка» (+20 % получаемого урона) не ложится на героя</t>
         </is>
       </c>
       <c r="K152" s="3" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «засветка»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «засветка» (−30 % магической защиты) не ложится на героя</t>
         </is>
       </c>
       <c r="K153" s="3" t="inlineStr">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «сброс»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «сброс» (пропуск хода и обнуление угрозы) не ложится на героя</t>
         </is>
       </c>
       <c r="K154" s="3" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «заморозка»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «заморозка» (пропуск хода, пока лёд цел) не ложится на героя</t>
         </is>
       </c>
       <c r="K155" s="3" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «осыпание»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «осыпание» (−30 % физической защиты) не ложится на героя</t>
         </is>
       </c>
       <c r="K156" s="3" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «слепота»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «слепота» (+50 % промахов) не ложится на героя</t>
         </is>
       </c>
       <c r="K157" s="3" t="inlineStr">
@@ -21968,7 +21968,7 @@
       <c r="E72" s="3"/>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «стужа»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «стужа» (−30 % скорости: цель ходит позже) не ложится на героя</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
@@ -22011,7 +22011,7 @@
       <c r="E73" s="3"/>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «истечение»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «истечение» (шансы способностей и ульты ×2/3) не ложится на героя</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
@@ -22054,7 +22054,7 @@
       <c r="E74" s="3"/>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «ослабление»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «ослабление» (−25 % урона) не ложится на героя</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -22097,7 +22097,7 @@
       <c r="E75" s="3"/>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «кровотечение»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «кровотечение» (урон в начале каждого её хода) не ложится на героя</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
@@ -22140,7 +22140,7 @@
       <c r="E76" s="3"/>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «метка»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «метка» (+20 % получаемого урона) не ложится на героя</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
@@ -22183,7 +22183,7 @@
       <c r="E77" s="3"/>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «засветка»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «засветка» (−30 % магической защиты) не ложится на героя</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
@@ -22226,7 +22226,7 @@
       <c r="E78" s="3"/>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «осыпание»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «осыпание» (−30 % физической защиты) не ложится на героя</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -22269,7 +22269,7 @@
       <c r="E79" s="3"/>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «слепота»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «слепота» (+50 % промахов) не ложится на героя</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
@@ -22312,7 +22312,7 @@
       <c r="E80" s="3"/>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «запрет способностей»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «запрет способностей» (только обычная атака) не ложится на героя</t>
         </is>
       </c>
       <c r="N80" s="3" t="inlineStr">
@@ -22355,7 +22355,7 @@
       <c r="E81" s="3"/>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «оглушение»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «оглушение» (пропуск хода) не ложится на героя</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
@@ -22398,7 +22398,7 @@
       <c r="E82" s="3"/>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «сброс»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «сброс» (пропуск хода и обнуление угрозы) не ложится на героя</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
@@ -22441,7 +22441,7 @@
       <c r="E83" s="3"/>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Защита от эффекта «заморозка»: он не ложится на героя</t>
+          <t xml:space="preserve">Эффект «заморозка» (пропуск хода, пока лёд цел) не ложится на героя</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">

--- a/source-data/Enerium_Талисманы_Финал.xlsx
+++ b/source-data/Enerium_Талисманы_Финал.xlsx
@@ -186,7 +186,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-06 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
+          <t xml:space="preserve">2026-10-07 — из данных игры сборщиком tools/content-gen/tables/build.py (содержимое — tools/content-gen/tables/collect.js)</t>
         </is>
       </c>
     </row>
@@ -198,7 +198,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">fc47f842f7aaa0ba — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
+          <t xml:space="preserve">509b5b0f21871410 — sha256 содержимого книги; по нему --check видит, что данные изменились</t>
         </is>
       </c>
     </row>
@@ -291,8 +291,8 @@
 III — слабые, почти незаметные намёки — слово-отзвук без имени тайны (ADR-0022: намёки на Странника — с цикла III)
 IV — заметнее, но всё ещё намёки: иносказание, без прямых имён и формулировок тайны
 V — намёки очевиднее («начиная с 5 будут намёки»); прямого раскрытия §38 нет
-VI — только для команды: здесь тайны названы прямо
-Ступени слов: D — прямое раскрытие — только цикл VI, для команды; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
+VI — раскрытие: в текстах игрока цикла VI тайны могут быть названы прямо (ADR-0054); в текстах циклов I–V — нет
+Ступени слов: D — прямое раскрытие — только с цикла VI: игрок получает его в игре, раньше — нет; H3 — явный намёк — с цикла V; H2 — заметный намёк — с цикла IV; H1 — слабый намёк, слово-отзвук — с цикла III.
 Проверка — node tools/content-gen/tables/check_spoilers.js; все совпадения по циклам — «Реестр имён», лист «Намёки по циклам».</t>
         </is>
       </c>
